--- a/data/publications/handbook-statistics-on-indian-economy/annual-series/output-and-prices/Index Numbers of Agricultural Production - Major Crops.xlsx
+++ b/data/publications/handbook-statistics-on-indian-economy/annual-series/output-and-prices/Index Numbers of Agricultural Production - Major Crops.xlsx
@@ -8,7 +8,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="142">
   <si>
     <t>Year</t>
   </si>
@@ -367,6 +367,9 @@
     <t>0.41</t>
   </si>
   <si>
+    <t xml:space="preserve">2025-26   </t>
+  </si>
+  <si>
     <t xml:space="preserve">2024-25   </t>
   </si>
   <si>
@@ -430,11 +433,12 @@
     <t>(Base : Triennium Ending 2007-08=100)</t>
   </si>
   <si>
-    <t xml:space="preserve">Notes : 1. Data for 2024-25 are based on Fourth Advance Estimates for Agricultural crops &amp; Second Advance Estimates for Horticultural Crops.
-            2. Oilseed data comprises of total oilseeds.
-            3. - : Not Available.
+    <t xml:space="preserve">Notes : 
+1. Data for 2025-26 are based on Third Advance Estimates for Agricultural Crops &amp; Second Advance Estimates for Horticultural Crops.
+2. Oilseed data comprises of total oilseeds.
+3. - : Not Available.
 Also see Notes on Tables.
-Source : Ministry of Agriculture, Government of India.</t>
+Source : Ministry of Agriculture &amp; Farmers Welfare, Government of India</t>
   </si>
 </sst>
 </file>
@@ -638,17 +642,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z69"/>
+  <dimension ref="A1:AA71"/>
   <cols>
     <col min="1" max="1" width="4.67767866666667" customWidth="1"/>
     <col min="2" max="2" width="13.1195986666667" customWidth="1"/>
     <col min="3" max="27" width="12.2639986666667" customWidth="1"/>
+    <col min="28" max="28" width="4.67767866666667" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="28.7982" customHeight="1"/>
     <row r="2" s="1" customFormat="1" ht="17.0656" customHeight="1">
       <c r="B2" s="13" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C2" s="13"/>
       <c r="D2" s="13"/>
@@ -661,7 +666,7 @@
     <row r="3" s="1" customFormat="1" ht="14.3991" customHeight="1"/>
     <row r="4" s="1" customFormat="1" ht="12.7992" customHeight="1">
       <c r="B4" s="14" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C4" s="14"/>
       <c r="D4" s="14"/>
@@ -2030,7 +2035,7 @@
     <row r="23" s="1" customFormat="1" ht="16.5323" customHeight="1"/>
     <row r="24" s="1" customFormat="1" ht="12.7992" customHeight="1">
       <c r="B24" s="14" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C24" s="14"/>
       <c r="D24" s="14"/>
@@ -3479,7 +3484,7 @@
     <row r="44" s="1" customFormat="1" ht="16.5323" customHeight="1"/>
     <row r="45" s="1" customFormat="1" ht="12.7992" customHeight="1">
       <c r="B45" s="14" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C45" s="14"/>
       <c r="D45" s="14"/>
@@ -3730,67 +3735,67 @@
         <v>119</v>
       </c>
       <c r="C50" s="8">
-        <v>167.538978</v>
+        <v>175.364738003</v>
       </c>
       <c r="D50" s="8">
-        <v>163.3</v>
+        <v>173.708202369</v>
       </c>
       <c r="E50" s="8">
-        <v>159.7</v>
+        <v>168.908843091</v>
       </c>
       <c r="F50" s="8">
-        <v>158.7</v>
+        <v>163.947685508</v>
       </c>
       <c r="G50" s="8">
-        <v>157.6</v>
+        <v>161.788720761</v>
       </c>
       <c r="H50" s="8">
-        <v>167.5</v>
+        <v>199.797383134</v>
       </c>
       <c r="I50" s="8">
-        <v>180.5</v>
+        <v>196.151269019</v>
       </c>
       <c r="J50" s="8">
-        <v>171.875092</v>
+        <v>177.068623696</v>
       </c>
       <c r="K50" s="8">
-        <v>154.4</v>
+        <v>159.228256995</v>
       </c>
       <c r="L50" s="8">
-        <v>161.9</v>
+        <v>177.966360093</v>
       </c>
       <c r="M50" s="8">
-        <v>123.4</v>
+        <v>139.000694307</v>
       </c>
       <c r="N50" s="8">
-        <v>176.7</v>
+        <v>192.987020269</v>
       </c>
       <c r="O50" s="8">
-        <v>134.8</v>
+        <v>133.424400947</v>
       </c>
       <c r="P50" s="8" t="s">
         <v>87</v>
       </c>
       <c r="Q50" s="8">
-        <v>137.4</v>
+        <v>129.929314227</v>
       </c>
       <c r="R50" s="8">
-        <v>82.9</v>
+        <v>90.236603762</v>
       </c>
       <c r="S50" s="8">
-        <v>123.9</v>
+        <v>139.756022236</v>
       </c>
       <c r="T50" s="8">
-        <v>132.2</v>
+        <v>146.723300971</v>
       </c>
       <c r="U50" s="8">
-        <v>105.8</v>
+        <v>109.440503064</v>
       </c>
       <c r="V50" s="8" t="s">
         <v>87</v>
       </c>
       <c r="W50" s="8">
-        <v>137.1</v>
+        <v>152.322174674</v>
       </c>
       <c r="X50" s="8" t="s">
         <v>87</v>
@@ -3810,73 +3815,73 @@
         <v>120</v>
       </c>
       <c r="C51" s="9">
-        <v>162.1</v>
+        <v>170.642420411</v>
       </c>
       <c r="D51" s="9">
-        <v>154.1</v>
+        <v>165.273078091</v>
       </c>
       <c r="E51" s="9">
-        <v>150.1</v>
+        <v>161.169773154</v>
       </c>
       <c r="F51" s="9">
-        <v>146.7</v>
+        <v>159.860283223</v>
       </c>
       <c r="G51" s="9">
-        <v>151.9</v>
+        <v>158.15103736</v>
       </c>
       <c r="H51" s="9">
-        <v>153.7</v>
+        <v>172.310808495</v>
       </c>
       <c r="I51" s="9">
-        <v>173</v>
+        <v>184.461211518</v>
       </c>
       <c r="J51" s="9">
-        <v>170.2</v>
+        <v>176.158294777</v>
       </c>
       <c r="K51" s="9">
-        <v>144.5</v>
+        <v>155.887334986</v>
       </c>
       <c r="L51" s="9">
-        <v>138.6</v>
+        <v>162.551396823</v>
       </c>
       <c r="M51" s="9">
-        <v>126</v>
+        <v>132.912616544</v>
       </c>
       <c r="N51" s="9">
-        <v>185.9</v>
+        <v>177.55473634</v>
       </c>
       <c r="O51" s="9">
-        <v>141.3</v>
+        <v>134.163626256</v>
       </c>
       <c r="P51" s="9" t="s">
         <v>87</v>
       </c>
       <c r="Q51" s="9">
-        <v>145.6</v>
+        <v>133.063751494</v>
       </c>
       <c r="R51" s="9">
-        <v>91</v>
+        <v>83.474712112</v>
       </c>
       <c r="S51" s="9">
-        <v>142.3</v>
+        <v>135.450895615</v>
       </c>
       <c r="T51" s="9">
-        <v>131.3</v>
+        <v>132.34223301</v>
       </c>
       <c r="U51" s="9">
-        <v>103.6</v>
+        <v>105.812641084</v>
       </c>
       <c r="V51" s="9" t="s">
         <v>87</v>
       </c>
       <c r="W51" s="9">
-        <v>138</v>
+        <v>138.477148573</v>
       </c>
       <c r="X51" s="9">
-        <v>184.2</v>
+        <v>220.633231908</v>
       </c>
       <c r="Y51" s="9">
-        <v>124.4</v>
+        <v>164.602186301</v>
       </c>
       <c r="Z51" s="9" t="s">
         <v>87</v>
@@ -3890,73 +3895,73 @@
         <v>121</v>
       </c>
       <c r="C52" s="8">
-        <v>165.2</v>
+        <v>162.1</v>
       </c>
       <c r="D52" s="8">
-        <v>154.6</v>
+        <v>154.1</v>
       </c>
       <c r="E52" s="8">
-        <v>147.8</v>
+        <v>150.1</v>
       </c>
       <c r="F52" s="8">
+        <v>146.7</v>
+      </c>
+      <c r="G52" s="8">
+        <v>151.9</v>
+      </c>
+      <c r="H52" s="8">
+        <v>153.7</v>
+      </c>
+      <c r="I52" s="8">
+        <v>173</v>
+      </c>
+      <c r="J52" s="8">
+        <v>170.2</v>
+      </c>
+      <c r="K52" s="8">
         <v>144.5</v>
       </c>
-      <c r="G52" s="8">
-        <v>148.2</v>
-      </c>
-      <c r="H52" s="8">
-        <v>154.5</v>
-      </c>
-      <c r="I52" s="8">
-        <v>186.6</v>
-      </c>
-      <c r="J52" s="8">
-        <v>176</v>
-      </c>
-      <c r="K52" s="8">
-        <v>149.2</v>
-      </c>
       <c r="L52" s="8">
-        <v>140.2</v>
+        <v>138.6</v>
       </c>
       <c r="M52" s="8">
-        <v>119.3</v>
+        <v>126</v>
       </c>
       <c r="N52" s="8">
-        <v>177.2</v>
+        <v>185.9</v>
       </c>
       <c r="O52" s="8">
-        <v>136</v>
+        <v>141.3</v>
       </c>
       <c r="P52" s="8" t="s">
         <v>87</v>
       </c>
       <c r="Q52" s="8">
-        <v>150.7</v>
+        <v>145.6</v>
       </c>
       <c r="R52" s="8">
-        <v>88.4</v>
+        <v>91</v>
       </c>
       <c r="S52" s="8">
-        <v>141.5</v>
+        <v>142.3</v>
       </c>
       <c r="T52" s="8">
-        <v>128.2</v>
+        <v>131.3</v>
       </c>
       <c r="U52" s="8">
-        <v>101.5</v>
+        <v>103.6</v>
       </c>
       <c r="V52" s="8" t="s">
         <v>87</v>
       </c>
       <c r="W52" s="8">
-        <v>149.4</v>
+        <v>138</v>
       </c>
       <c r="X52" s="8">
-        <v>163.8</v>
+        <v>184.2</v>
       </c>
       <c r="Y52" s="8">
-        <v>133.5</v>
+        <v>124.4</v>
       </c>
       <c r="Z52" s="8" t="s">
         <v>87</v>
@@ -3970,73 +3975,73 @@
         <v>122</v>
       </c>
       <c r="C53" s="9">
-        <v>158</v>
+        <v>165.2</v>
       </c>
       <c r="D53" s="9">
-        <v>150.2</v>
+        <v>154.6</v>
       </c>
       <c r="E53" s="9">
-        <v>140.7</v>
+        <v>147.8</v>
       </c>
       <c r="F53" s="9">
-        <v>137.8</v>
+        <v>144.5</v>
       </c>
       <c r="G53" s="9">
-        <v>144.5</v>
+        <v>148.2</v>
       </c>
       <c r="H53" s="9">
-        <v>137.9</v>
+        <v>154.5</v>
       </c>
       <c r="I53" s="9">
-        <v>194.5</v>
+        <v>186.6</v>
       </c>
       <c r="J53" s="9">
-        <v>166.1</v>
+        <v>176</v>
       </c>
       <c r="K53" s="9">
-        <v>138</v>
+        <v>149.2</v>
       </c>
       <c r="L53" s="9">
-        <v>138</v>
+        <v>140.2</v>
       </c>
       <c r="M53" s="9">
-        <v>117.3</v>
+        <v>119.3</v>
       </c>
       <c r="N53" s="9">
-        <v>167.7</v>
+        <v>177.2</v>
       </c>
       <c r="O53" s="9">
-        <v>127.9</v>
+        <v>136</v>
       </c>
       <c r="P53" s="9" t="s">
         <v>87</v>
       </c>
       <c r="Q53" s="9">
-        <v>139.3</v>
+        <v>150.7</v>
       </c>
       <c r="R53" s="9">
-        <v>96</v>
+        <v>88.4</v>
       </c>
       <c r="S53" s="9">
-        <v>138.4</v>
+        <v>141.5</v>
       </c>
       <c r="T53" s="9">
-        <v>124.5</v>
+        <v>128.2</v>
       </c>
       <c r="U53" s="9">
-        <v>93.7</v>
+        <v>101.5</v>
       </c>
       <c r="V53" s="9" t="s">
         <v>87</v>
       </c>
       <c r="W53" s="9">
-        <v>133.9</v>
+        <v>149.4</v>
       </c>
       <c r="X53" s="9">
-        <v>174</v>
+        <v>163.8</v>
       </c>
       <c r="Y53" s="9">
-        <v>88.4</v>
+        <v>133.5</v>
       </c>
       <c r="Z53" s="9" t="s">
         <v>87</v>
@@ -4050,73 +4055,73 @@
         <v>123</v>
       </c>
       <c r="C54" s="8">
-        <v>154.1</v>
+        <v>158</v>
       </c>
       <c r="D54" s="8">
-        <v>147</v>
+        <v>150.2</v>
       </c>
       <c r="E54" s="8">
-        <v>139.7</v>
+        <v>140.7</v>
       </c>
       <c r="F54" s="8">
-        <v>132.4</v>
+        <v>137.8</v>
       </c>
       <c r="G54" s="8">
-        <v>146.9</v>
+        <v>144.5</v>
       </c>
       <c r="H54" s="8">
-        <v>139</v>
+        <v>137.9</v>
       </c>
       <c r="I54" s="8">
-        <v>181.1</v>
+        <v>194.5</v>
       </c>
       <c r="J54" s="8">
-        <v>161.3</v>
+        <v>166.1</v>
       </c>
       <c r="K54" s="8">
-        <v>130.7</v>
+        <v>138</v>
       </c>
       <c r="L54" s="8">
-        <v>139.4</v>
+        <v>138</v>
       </c>
       <c r="M54" s="8">
-        <v>121.5</v>
+        <v>117.3</v>
       </c>
       <c r="N54" s="8">
-        <v>143.1</v>
+        <v>167.7</v>
       </c>
       <c r="O54" s="8">
-        <v>137.3</v>
+        <v>127.9</v>
       </c>
       <c r="P54" s="8" t="s">
         <v>87</v>
       </c>
       <c r="Q54" s="8">
-        <v>157.8</v>
+        <v>139.3</v>
       </c>
       <c r="R54" s="8">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="S54" s="8">
-        <v>132.1</v>
+        <v>138.4</v>
       </c>
       <c r="T54" s="8">
-        <v>121.6</v>
+        <v>124.5</v>
       </c>
       <c r="U54" s="8">
-        <v>86.5</v>
+        <v>93.7</v>
       </c>
       <c r="V54" s="8" t="s">
         <v>87</v>
       </c>
       <c r="W54" s="8">
-        <v>123.5</v>
+        <v>133.9</v>
       </c>
       <c r="X54" s="8">
-        <v>160.7</v>
+        <v>174</v>
       </c>
       <c r="Y54" s="8">
-        <v>97.2</v>
+        <v>88.4</v>
       </c>
       <c r="Z54" s="8" t="s">
         <v>87</v>
@@ -4130,73 +4135,73 @@
         <v>124</v>
       </c>
       <c r="C55" s="9">
-        <v>145.5</v>
+        <v>154.1</v>
       </c>
       <c r="D55" s="9">
-        <v>139.8</v>
+        <v>147</v>
       </c>
       <c r="E55" s="9">
-        <v>134.8</v>
+        <v>139.7</v>
       </c>
       <c r="F55" s="9">
-        <v>126.5</v>
+        <v>132.4</v>
       </c>
       <c r="G55" s="9">
-        <v>144.6</v>
+        <v>146.9</v>
       </c>
       <c r="H55" s="9">
-        <v>129.5</v>
+        <v>139</v>
       </c>
       <c r="I55" s="9">
-        <v>163.3</v>
+        <v>181.1</v>
       </c>
       <c r="J55" s="9">
-        <v>151.3</v>
+        <v>161.3</v>
       </c>
       <c r="K55" s="9">
-        <v>121.3</v>
+        <v>130.7</v>
       </c>
       <c r="L55" s="9">
-        <v>135.5</v>
+        <v>139.4</v>
       </c>
       <c r="M55" s="9">
-        <v>97.8</v>
+        <v>121.5</v>
       </c>
       <c r="N55" s="9">
-        <v>127.9</v>
+        <v>143.1</v>
       </c>
       <c r="O55" s="9">
-        <v>134.5</v>
+        <v>137.3</v>
       </c>
       <c r="P55" s="9" t="s">
         <v>87</v>
       </c>
       <c r="Q55" s="9">
-        <v>161.4</v>
+        <v>157.8</v>
       </c>
       <c r="R55" s="9">
-        <v>92.9</v>
+        <v>88</v>
       </c>
       <c r="S55" s="9">
-        <v>140.1</v>
+        <v>132.1</v>
       </c>
       <c r="T55" s="9">
-        <v>108.5</v>
+        <v>121.6</v>
       </c>
       <c r="U55" s="9">
-        <v>86.1</v>
+        <v>86.5</v>
       </c>
       <c r="V55" s="9" t="s">
         <v>87</v>
       </c>
       <c r="W55" s="9">
-        <v>112.9</v>
+        <v>123.5</v>
       </c>
       <c r="X55" s="9">
-        <v>170.5</v>
+        <v>160.7</v>
       </c>
       <c r="Y55" s="9">
-        <v>113.5</v>
+        <v>97.2</v>
       </c>
       <c r="Z55" s="9" t="s">
         <v>87</v>
@@ -4210,73 +4215,73 @@
         <v>125</v>
       </c>
       <c r="C56" s="8">
-        <v>138.1</v>
+        <v>145.5</v>
       </c>
       <c r="D56" s="8">
-        <v>134.4</v>
+        <v>139.8</v>
       </c>
       <c r="E56" s="8">
-        <v>129.2</v>
+        <v>134.8</v>
       </c>
       <c r="F56" s="8">
-        <v>124</v>
+        <v>126.5</v>
       </c>
       <c r="G56" s="8">
-        <v>138.9</v>
+        <v>144.6</v>
       </c>
       <c r="H56" s="8">
-        <v>116.4</v>
+        <v>129.5</v>
       </c>
       <c r="I56" s="8">
-        <v>158.9</v>
+        <v>163.3</v>
       </c>
       <c r="J56" s="8">
-        <v>142</v>
+        <v>151.3</v>
       </c>
       <c r="K56" s="8">
-        <v>111.6</v>
+        <v>121.3</v>
       </c>
       <c r="L56" s="8">
-        <v>91.6</v>
+        <v>135.5</v>
       </c>
       <c r="M56" s="8">
-        <v>102.6</v>
+        <v>97.8</v>
       </c>
       <c r="N56" s="8">
-        <v>129.7</v>
+        <v>127.9</v>
       </c>
       <c r="O56" s="8">
-        <v>141</v>
+        <v>134.5</v>
       </c>
       <c r="P56" s="8" t="s">
         <v>87</v>
       </c>
       <c r="Q56" s="8">
-        <v>125.5</v>
+        <v>161.4</v>
       </c>
       <c r="R56" s="8">
-        <v>93.4</v>
+        <v>92.9</v>
       </c>
       <c r="S56" s="8">
-        <v>139</v>
+        <v>140.1</v>
       </c>
       <c r="T56" s="8">
-        <v>116.3</v>
+        <v>108.5</v>
       </c>
       <c r="U56" s="8">
-        <v>78.7</v>
+        <v>86.1</v>
       </c>
       <c r="V56" s="8" t="s">
         <v>87</v>
       </c>
       <c r="W56" s="8">
-        <v>123.5</v>
+        <v>112.9</v>
       </c>
       <c r="X56" s="8">
-        <v>140</v>
+        <v>170.5</v>
       </c>
       <c r="Y56" s="8">
-        <v>98</v>
+        <v>113.5</v>
       </c>
       <c r="Z56" s="8" t="s">
         <v>87</v>
@@ -4290,73 +4295,73 @@
         <v>126</v>
       </c>
       <c r="C57" s="9">
-        <v>139.4</v>
+        <v>138.1</v>
       </c>
       <c r="D57" s="9">
-        <v>136.8</v>
+        <v>134.4</v>
       </c>
       <c r="E57" s="9">
-        <v>127.2</v>
+        <v>129.2</v>
       </c>
       <c r="F57" s="9">
-        <v>120.2</v>
+        <v>124</v>
       </c>
       <c r="G57" s="9">
-        <v>133.9</v>
+        <v>138.9</v>
       </c>
       <c r="H57" s="9">
-        <v>127.3</v>
+        <v>116.4</v>
       </c>
       <c r="I57" s="9">
-        <v>181.7</v>
+        <v>158.9</v>
       </c>
       <c r="J57" s="9">
-        <v>142.1</v>
+        <v>142</v>
       </c>
       <c r="K57" s="9">
-        <v>114.7</v>
+        <v>111.6</v>
       </c>
       <c r="L57" s="9">
-        <v>125.9</v>
+        <v>91.6</v>
       </c>
       <c r="M57" s="9">
-        <v>112.4</v>
+        <v>102.6</v>
       </c>
       <c r="N57" s="9">
-        <v>118.2</v>
+        <v>129.7</v>
       </c>
       <c r="O57" s="9">
-        <v>157.6</v>
+        <v>141</v>
       </c>
       <c r="P57" s="9" t="s">
         <v>87</v>
       </c>
       <c r="Q57" s="9">
-        <v>146.9</v>
+        <v>125.5</v>
       </c>
       <c r="R57" s="9">
-        <v>94.3</v>
+        <v>93.4</v>
       </c>
       <c r="S57" s="9">
-        <v>136.4</v>
+        <v>139</v>
       </c>
       <c r="T57" s="9">
-        <v>115</v>
+        <v>116.3</v>
       </c>
       <c r="U57" s="9">
-        <v>83.9</v>
+        <v>78.7</v>
       </c>
       <c r="V57" s="9" t="s">
         <v>87</v>
       </c>
       <c r="W57" s="9">
-        <v>115.7</v>
+        <v>123.5</v>
       </c>
       <c r="X57" s="9">
-        <v>202.4</v>
+        <v>140</v>
       </c>
       <c r="Y57" s="9">
-        <v>121.3</v>
+        <v>98</v>
       </c>
       <c r="Z57" s="9" t="s">
         <v>87</v>
@@ -4370,73 +4375,73 @@
         <v>127</v>
       </c>
       <c r="C58" s="8">
-        <v>132.8</v>
+        <v>139.4</v>
       </c>
       <c r="D58" s="8">
-        <v>131.1</v>
+        <v>136.8</v>
       </c>
       <c r="E58" s="8">
-        <v>123.7</v>
+        <v>127.2</v>
       </c>
       <c r="F58" s="8">
-        <v>116.8</v>
+        <v>120.2</v>
       </c>
       <c r="G58" s="8">
-        <v>132.1</v>
+        <v>133.9</v>
       </c>
       <c r="H58" s="8">
-        <v>118.8</v>
+        <v>127.3</v>
       </c>
       <c r="I58" s="8">
-        <v>165.5</v>
+        <v>181.7</v>
       </c>
       <c r="J58" s="8">
-        <v>134.7</v>
+        <v>142.1</v>
       </c>
       <c r="K58" s="8">
-        <v>111.2</v>
+        <v>114.7</v>
       </c>
       <c r="L58" s="8">
-        <v>101.6</v>
+        <v>125.9</v>
       </c>
       <c r="M58" s="8">
-        <v>111.1</v>
+        <v>112.4</v>
       </c>
       <c r="N58" s="8">
-        <v>111</v>
+        <v>118.2</v>
       </c>
       <c r="O58" s="8">
-        <v>158.3</v>
+        <v>157.6</v>
       </c>
       <c r="P58" s="8" t="s">
         <v>87</v>
       </c>
       <c r="Q58" s="8">
-        <v>145.8</v>
+        <v>146.9</v>
       </c>
       <c r="R58" s="8">
-        <v>102.6</v>
+        <v>94.3</v>
       </c>
       <c r="S58" s="8">
-        <v>128.7</v>
+        <v>136.4</v>
       </c>
       <c r="T58" s="8">
-        <v>113.6</v>
+        <v>115</v>
       </c>
       <c r="U58" s="8">
-        <v>83.6</v>
+        <v>83.9</v>
       </c>
       <c r="V58" s="8" t="s">
         <v>87</v>
       </c>
       <c r="W58" s="8">
-        <v>93.2</v>
+        <v>115.7</v>
       </c>
       <c r="X58" s="8">
-        <v>171.4</v>
+        <v>202.4</v>
       </c>
       <c r="Y58" s="8">
-        <v>138.1</v>
+        <v>121.3</v>
       </c>
       <c r="Z58" s="8" t="s">
         <v>87</v>
@@ -4450,73 +4455,73 @@
         <v>128</v>
       </c>
       <c r="C59" s="9">
-        <v>120.8</v>
+        <v>132.8</v>
       </c>
       <c r="D59" s="9">
-        <v>115.7</v>
+        <v>131.1</v>
       </c>
       <c r="E59" s="9">
-        <v>115.5</v>
+        <v>123.7</v>
       </c>
       <c r="F59" s="9">
+        <v>116.8</v>
+      </c>
+      <c r="G59" s="9">
+        <v>132.1</v>
+      </c>
+      <c r="H59" s="9">
+        <v>118.8</v>
+      </c>
+      <c r="I59" s="9">
+        <v>165.5</v>
+      </c>
+      <c r="J59" s="9">
+        <v>134.7</v>
+      </c>
+      <c r="K59" s="9">
+        <v>111.2</v>
+      </c>
+      <c r="L59" s="9">
+        <v>101.6</v>
+      </c>
+      <c r="M59" s="9">
         <v>111.1</v>
       </c>
-      <c r="G59" s="9">
-        <v>123.7</v>
-      </c>
-      <c r="H59" s="9">
-        <v>104.6</v>
-      </c>
-      <c r="I59" s="9">
-        <v>116.7</v>
-      </c>
-      <c r="J59" s="9">
-        <v>126.1</v>
-      </c>
-      <c r="K59" s="9">
-        <v>92.5</v>
-      </c>
-      <c r="L59" s="9">
-        <v>91.7</v>
-      </c>
-      <c r="M59" s="9">
-        <v>126.5</v>
-      </c>
       <c r="N59" s="9">
-        <v>95.3</v>
+        <v>111</v>
       </c>
       <c r="O59" s="9">
-        <v>146.5</v>
+        <v>158.3</v>
       </c>
       <c r="P59" s="9" t="s">
         <v>87</v>
       </c>
       <c r="Q59" s="9">
-        <v>134.3</v>
+        <v>145.8</v>
       </c>
       <c r="R59" s="9">
-        <v>97.8</v>
+        <v>102.6</v>
       </c>
       <c r="S59" s="9">
-        <v>126.9</v>
+        <v>128.7</v>
       </c>
       <c r="T59" s="9">
-        <v>126.7</v>
+        <v>113.6</v>
       </c>
       <c r="U59" s="9">
-        <v>68</v>
+        <v>83.6</v>
       </c>
       <c r="V59" s="9" t="s">
         <v>87</v>
       </c>
       <c r="W59" s="9">
-        <v>106.1</v>
+        <v>93.2</v>
       </c>
       <c r="X59" s="9">
-        <v>170.8</v>
+        <v>171.4</v>
       </c>
       <c r="Y59" s="9">
-        <v>211</v>
+        <v>138.1</v>
       </c>
       <c r="Z59" s="9" t="s">
         <v>87</v>
@@ -4530,73 +4535,73 @@
         <v>129</v>
       </c>
       <c r="C60" s="8">
-        <v>124</v>
+        <v>120.8</v>
       </c>
       <c r="D60" s="8">
-        <v>115.9</v>
+        <v>115.7</v>
       </c>
       <c r="E60" s="8">
-        <v>114.6</v>
+        <v>115.5</v>
       </c>
       <c r="F60" s="8">
-        <v>112.3</v>
+        <v>111.1</v>
       </c>
       <c r="G60" s="8">
-        <v>116</v>
+        <v>123.7</v>
       </c>
       <c r="H60" s="8">
+        <v>104.6</v>
+      </c>
+      <c r="I60" s="8">
         <v>116.7</v>
       </c>
-      <c r="I60" s="8">
-        <v>122</v>
-      </c>
       <c r="J60" s="8">
-        <v>132.3</v>
+        <v>126.1</v>
       </c>
       <c r="K60" s="8">
-        <v>99.7</v>
+        <v>92.5</v>
       </c>
       <c r="L60" s="8">
-        <v>100.8</v>
+        <v>91.7</v>
       </c>
       <c r="M60" s="8">
-        <v>123.2</v>
+        <v>126.5</v>
       </c>
       <c r="N60" s="8">
-        <v>88.1</v>
+        <v>95.3</v>
       </c>
       <c r="O60" s="8">
-        <v>135.1</v>
+        <v>146.5</v>
       </c>
       <c r="P60" s="8" t="s">
         <v>87</v>
       </c>
       <c r="Q60" s="8">
-        <v>155.8</v>
+        <v>134.3</v>
       </c>
       <c r="R60" s="8">
-        <v>104.4</v>
+        <v>97.8</v>
       </c>
       <c r="S60" s="8">
-        <v>123.2</v>
+        <v>126.9</v>
       </c>
       <c r="T60" s="8">
-        <v>119.1</v>
+        <v>126.7</v>
       </c>
       <c r="U60" s="8">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="V60" s="8" t="s">
         <v>87</v>
       </c>
       <c r="W60" s="8">
-        <v>110.4</v>
+        <v>106.1</v>
       </c>
       <c r="X60" s="8">
-        <v>182</v>
+        <v>170.8</v>
       </c>
       <c r="Y60" s="8">
-        <v>244.7</v>
+        <v>211</v>
       </c>
       <c r="Z60" s="8" t="s">
         <v>87</v>
@@ -4610,73 +4615,73 @@
         <v>130</v>
       </c>
       <c r="C61" s="9">
-        <v>129.8</v>
+        <v>124</v>
       </c>
       <c r="D61" s="9">
-        <v>123.3</v>
+        <v>115.9</v>
       </c>
       <c r="E61" s="9">
-        <v>120.7</v>
+        <v>114.6</v>
       </c>
       <c r="F61" s="9">
-        <v>113.5</v>
+        <v>112.3</v>
       </c>
       <c r="G61" s="9">
-        <v>128.5</v>
+        <v>116</v>
       </c>
       <c r="H61" s="9">
-        <v>118</v>
+        <v>116.7</v>
       </c>
       <c r="I61" s="9">
-        <v>135.6</v>
+        <v>122</v>
       </c>
       <c r="J61" s="9">
-        <v>136.4</v>
+        <v>132.3</v>
       </c>
       <c r="K61" s="9">
-        <v>119</v>
+        <v>99.7</v>
       </c>
       <c r="L61" s="9">
-        <v>132.2</v>
+        <v>100.8</v>
       </c>
       <c r="M61" s="9">
-        <v>106.3</v>
+        <v>123.2</v>
       </c>
       <c r="N61" s="9">
+        <v>88.1</v>
+      </c>
+      <c r="O61" s="9">
+        <v>135.1</v>
+      </c>
+      <c r="P61" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q61" s="9">
+        <v>155.8</v>
+      </c>
+      <c r="R61" s="9">
+        <v>104.4</v>
+      </c>
+      <c r="S61" s="9">
+        <v>123.2</v>
+      </c>
+      <c r="T61" s="9">
+        <v>119.1</v>
+      </c>
+      <c r="U61" s="9">
+        <v>78</v>
+      </c>
+      <c r="V61" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="W61" s="9">
         <v>110.4</v>
       </c>
-      <c r="O61" s="9">
-        <v>154.2</v>
-      </c>
-      <c r="P61" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="Q61" s="9">
-        <v>160.7</v>
-      </c>
-      <c r="R61" s="9">
-        <v>109</v>
-      </c>
-      <c r="S61" s="9">
-        <v>124.4</v>
-      </c>
-      <c r="T61" s="9">
-        <v>110.9</v>
-      </c>
-      <c r="U61" s="9">
-        <v>93.6</v>
-      </c>
-      <c r="V61" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="W61" s="9">
-        <v>107.3</v>
-      </c>
       <c r="X61" s="9">
-        <v>156.4</v>
+        <v>182</v>
       </c>
       <c r="Y61" s="9">
-        <v>267.8</v>
+        <v>244.7</v>
       </c>
       <c r="Z61" s="9" t="s">
         <v>87</v>
@@ -4690,73 +4695,73 @@
         <v>131</v>
       </c>
       <c r="C62" s="8">
-        <v>124.2</v>
+        <v>129.8</v>
       </c>
       <c r="D62" s="8">
-        <v>119.4</v>
+        <v>123.3</v>
       </c>
       <c r="E62" s="8">
-        <v>117.3</v>
+        <v>120.7</v>
       </c>
       <c r="F62" s="8">
-        <v>112</v>
+        <v>113.5</v>
       </c>
       <c r="G62" s="8">
-        <v>125.4</v>
+        <v>128.5</v>
       </c>
       <c r="H62" s="8">
-        <v>109.2</v>
+        <v>118</v>
       </c>
       <c r="I62" s="8">
-        <v>129.4</v>
+        <v>135.6</v>
       </c>
       <c r="J62" s="8">
-        <v>129</v>
+        <v>136.4</v>
       </c>
       <c r="K62" s="8">
-        <v>107.4</v>
+        <v>119</v>
       </c>
       <c r="L62" s="8">
-        <v>63.9</v>
+        <v>132.2</v>
       </c>
       <c r="M62" s="8">
-        <v>101.9</v>
+        <v>106.3</v>
       </c>
       <c r="N62" s="8">
-        <v>112.5</v>
+        <v>110.4</v>
       </c>
       <c r="O62" s="8">
-        <v>149.9</v>
+        <v>154.2</v>
       </c>
       <c r="P62" s="8" t="s">
         <v>87</v>
       </c>
       <c r="Q62" s="8">
-        <v>153.2</v>
+        <v>160.7</v>
       </c>
       <c r="R62" s="8">
-        <v>101.7</v>
+        <v>109</v>
       </c>
       <c r="S62" s="8">
-        <v>101</v>
+        <v>124.4</v>
       </c>
       <c r="T62" s="8">
-        <v>110</v>
+        <v>110.9</v>
       </c>
       <c r="U62" s="8">
-        <v>100.4</v>
+        <v>93.6</v>
       </c>
       <c r="V62" s="8" t="s">
         <v>87</v>
       </c>
       <c r="W62" s="8">
-        <v>103.9</v>
+        <v>107.3</v>
       </c>
       <c r="X62" s="8">
-        <v>139.8</v>
+        <v>156.4</v>
       </c>
       <c r="Y62" s="8">
-        <v>183.6</v>
+        <v>267.8</v>
       </c>
       <c r="Z62" s="8" t="s">
         <v>87</v>
@@ -4770,52 +4775,52 @@
         <v>132</v>
       </c>
       <c r="C63" s="9">
-        <v>124.3</v>
+        <v>124.2</v>
       </c>
       <c r="D63" s="9">
-        <v>119.5</v>
+        <v>119.4</v>
       </c>
       <c r="E63" s="9">
-        <v>119.1</v>
+        <v>117.3</v>
       </c>
       <c r="F63" s="9">
-        <v>112.1</v>
+        <v>112</v>
       </c>
       <c r="G63" s="9">
-        <v>127.2</v>
+        <v>125.4</v>
       </c>
       <c r="H63" s="9">
-        <v>114.8</v>
+        <v>109.2</v>
       </c>
       <c r="I63" s="9">
-        <v>121.6</v>
+        <v>129.4</v>
       </c>
       <c r="J63" s="9">
-        <v>129.3</v>
+        <v>129</v>
       </c>
       <c r="K63" s="9">
-        <v>106.5</v>
+        <v>107.4</v>
       </c>
       <c r="L63" s="9">
-        <v>94.8</v>
+        <v>63.9</v>
       </c>
       <c r="M63" s="9">
-        <v>120.6</v>
+        <v>101.9</v>
       </c>
       <c r="N63" s="9">
-        <v>92.6</v>
+        <v>112.5</v>
       </c>
       <c r="O63" s="9">
-        <v>104.1</v>
+        <v>149.9</v>
       </c>
       <c r="P63" s="9" t="s">
         <v>87</v>
       </c>
       <c r="Q63" s="9">
-        <v>157.6</v>
+        <v>153.2</v>
       </c>
       <c r="R63" s="9">
-        <v>105.6</v>
+        <v>101.7</v>
       </c>
       <c r="S63" s="9">
         <v>101</v>
@@ -4824,19 +4829,19 @@
         <v>110</v>
       </c>
       <c r="U63" s="9">
-        <v>100.5</v>
+        <v>100.4</v>
       </c>
       <c r="V63" s="9" t="s">
         <v>87</v>
       </c>
       <c r="W63" s="9">
-        <v>110</v>
+        <v>103.9</v>
       </c>
       <c r="X63" s="9">
-        <v>160</v>
+        <v>139.8</v>
       </c>
       <c r="Y63" s="9">
-        <v>165.6</v>
+        <v>183.6</v>
       </c>
       <c r="Z63" s="9" t="s">
         <v>87</v>
@@ -4850,40 +4855,40 @@
         <v>133</v>
       </c>
       <c r="C64" s="8">
-        <v>121</v>
+        <v>124.3</v>
       </c>
       <c r="D64" s="8">
-        <v>114.3</v>
+        <v>119.5</v>
       </c>
       <c r="E64" s="8">
-        <v>111.1</v>
+        <v>119.1</v>
       </c>
       <c r="F64" s="8">
-        <v>102.2</v>
+        <v>112.1</v>
       </c>
       <c r="G64" s="8">
-        <v>116.5</v>
+        <v>127.2</v>
       </c>
       <c r="H64" s="8">
-        <v>118.9</v>
+        <v>114.8</v>
       </c>
       <c r="I64" s="8">
-        <v>129.4</v>
+        <v>121.6</v>
       </c>
       <c r="J64" s="8">
-        <v>128</v>
+        <v>129.3</v>
       </c>
       <c r="K64" s="8">
-        <v>116.8</v>
+        <v>106.5</v>
       </c>
       <c r="L64" s="8">
-        <v>112.5</v>
+        <v>94.8</v>
       </c>
       <c r="M64" s="8">
-        <v>132.9</v>
+        <v>120.6</v>
       </c>
       <c r="N64" s="8">
-        <v>114.6</v>
+        <v>92.6</v>
       </c>
       <c r="O64" s="8">
         <v>104.1</v>
@@ -4892,10 +4897,10 @@
         <v>87</v>
       </c>
       <c r="Q64" s="8">
-        <v>147.7</v>
+        <v>157.6</v>
       </c>
       <c r="R64" s="8">
-        <v>98.4</v>
+        <v>105.6</v>
       </c>
       <c r="S64" s="8">
         <v>101</v>
@@ -4910,13 +4915,13 @@
         <v>87</v>
       </c>
       <c r="W64" s="8">
-        <v>104.3</v>
+        <v>110</v>
       </c>
       <c r="X64" s="8">
-        <v>176.9</v>
+        <v>160</v>
       </c>
       <c r="Y64" s="8">
-        <v>147.2</v>
+        <v>165.6</v>
       </c>
       <c r="Z64" s="8" t="s">
         <v>87</v>
@@ -4930,58 +4935,58 @@
         <v>134</v>
       </c>
       <c r="C65" s="9">
-        <v>102.7</v>
+        <v>121</v>
       </c>
       <c r="D65" s="9">
-        <v>100.6</v>
+        <v>114.3</v>
       </c>
       <c r="E65" s="9">
-        <v>100.2</v>
+        <v>111.1</v>
       </c>
       <c r="F65" s="9">
-        <v>94.8</v>
+        <v>102.2</v>
       </c>
       <c r="G65" s="9">
-        <v>108.3</v>
+        <v>116.5</v>
       </c>
       <c r="H65" s="9">
-        <v>92.3</v>
+        <v>118.9</v>
       </c>
       <c r="I65" s="9">
-        <v>102.3</v>
+        <v>129.4</v>
       </c>
       <c r="J65" s="9">
-        <v>104.9</v>
+        <v>128</v>
       </c>
       <c r="K65" s="9">
-        <v>88.9</v>
+        <v>116.8</v>
       </c>
       <c r="L65" s="9">
-        <v>73.9</v>
+        <v>112.5</v>
       </c>
       <c r="M65" s="9">
-        <v>87.5</v>
+        <v>132.9</v>
       </c>
       <c r="N65" s="9">
-        <v>92.6</v>
+        <v>114.6</v>
       </c>
       <c r="O65" s="9">
-        <v>104</v>
+        <v>104.1</v>
       </c>
       <c r="P65" s="9" t="s">
         <v>87</v>
       </c>
       <c r="Q65" s="9">
-        <v>107.5</v>
+        <v>147.7</v>
       </c>
       <c r="R65" s="9">
-        <v>110.4</v>
+        <v>98.4</v>
       </c>
       <c r="S65" s="9">
         <v>101</v>
       </c>
       <c r="T65" s="9">
-        <v>105.4</v>
+        <v>110</v>
       </c>
       <c r="U65" s="9">
         <v>100.5</v>
@@ -4990,13 +4995,13 @@
         <v>87</v>
       </c>
       <c r="W65" s="9">
-        <v>89</v>
+        <v>104.3</v>
       </c>
       <c r="X65" s="9">
-        <v>147.4</v>
+        <v>176.9</v>
       </c>
       <c r="Y65" s="9">
-        <v>44.3</v>
+        <v>147.2</v>
       </c>
       <c r="Z65" s="9" t="s">
         <v>87</v>
@@ -5010,181 +5015,262 @@
         <v>135</v>
       </c>
       <c r="C66" s="8">
-        <v>107</v>
+        <v>102.7</v>
       </c>
       <c r="D66" s="8">
-        <v>106.5</v>
+        <v>100.6</v>
       </c>
       <c r="E66" s="8">
-        <v>107.4</v>
+        <v>100.2</v>
       </c>
       <c r="F66" s="8">
-        <v>105.6</v>
+        <v>94.8</v>
       </c>
       <c r="G66" s="8">
-        <v>108.2</v>
+        <v>108.3</v>
       </c>
       <c r="H66" s="8">
-        <v>110</v>
+        <v>92.3</v>
       </c>
       <c r="I66" s="8">
-        <v>102</v>
+        <v>102.3</v>
       </c>
       <c r="J66" s="8">
-        <v>107.6</v>
+        <v>104.9</v>
       </c>
       <c r="K66" s="8">
-        <v>100.8</v>
+        <v>88.9</v>
       </c>
       <c r="L66" s="8">
-        <v>97.6</v>
+        <v>73.9</v>
       </c>
       <c r="M66" s="8">
-        <v>95.3</v>
+        <v>87.5</v>
       </c>
       <c r="N66" s="8">
-        <v>100.9</v>
+        <v>92.6</v>
       </c>
       <c r="O66" s="8">
-        <v>97.5</v>
+        <v>104</v>
       </c>
       <c r="P66" s="8" t="s">
         <v>87</v>
       </c>
       <c r="Q66" s="8">
-        <v>99.7</v>
+        <v>107.5</v>
       </c>
       <c r="R66" s="8">
-        <v>94.7</v>
+        <v>110.4</v>
       </c>
       <c r="S66" s="8">
         <v>101</v>
       </c>
       <c r="T66" s="8">
+        <v>105.4</v>
+      </c>
+      <c r="U66" s="8">
+        <v>100.5</v>
+      </c>
+      <c r="V66" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="W66" s="8">
+        <v>89</v>
+      </c>
+      <c r="X66" s="8">
+        <v>147.4</v>
+      </c>
+      <c r="Y66" s="8">
+        <v>44.3</v>
+      </c>
+      <c r="Z66" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="AA66" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="67" s="1" customFormat="1" ht="14.3991" customHeight="1">
+      <c r="B67" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="C67" s="9">
+        <v>107</v>
+      </c>
+      <c r="D67" s="9">
+        <v>106.5</v>
+      </c>
+      <c r="E67" s="9">
+        <v>107.4</v>
+      </c>
+      <c r="F67" s="9">
+        <v>105.6</v>
+      </c>
+      <c r="G67" s="9">
+        <v>108.2</v>
+      </c>
+      <c r="H67" s="9">
+        <v>110</v>
+      </c>
+      <c r="I67" s="9">
+        <v>102</v>
+      </c>
+      <c r="J67" s="9">
+        <v>107.6</v>
+      </c>
+      <c r="K67" s="9">
+        <v>100.8</v>
+      </c>
+      <c r="L67" s="9">
+        <v>97.6</v>
+      </c>
+      <c r="M67" s="9">
+        <v>95.3</v>
+      </c>
+      <c r="N67" s="9">
+        <v>100.9</v>
+      </c>
+      <c r="O67" s="9">
+        <v>97.5</v>
+      </c>
+      <c r="P67" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q67" s="9">
+        <v>99.7</v>
+      </c>
+      <c r="R67" s="9">
+        <v>94.7</v>
+      </c>
+      <c r="S67" s="9">
+        <v>101</v>
+      </c>
+      <c r="T67" s="9">
         <v>95.5</v>
       </c>
-      <c r="U66" s="8">
+      <c r="U67" s="9">
         <v>104.5</v>
       </c>
-      <c r="V66" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="W66" s="8">
+      <c r="V67" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="W67" s="9">
         <v>86.8</v>
       </c>
-      <c r="X66" s="8">
+      <c r="X67" s="9">
         <v>121</v>
       </c>
-      <c r="Y66" s="8">
+      <c r="Y67" s="9">
         <v>144.6</v>
       </c>
-      <c r="Z66" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="AA66" s="8" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="67" s="1" customFormat="1" ht="14.3991" customHeight="1">
-      <c r="B67" s="10" t="s">
+      <c r="Z67" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="AA67" s="9" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="68" s="1" customFormat="1" ht="14.3991" customHeight="1">
+      <c r="B68" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="C67" s="11">
+      <c r="C68" s="12">
         <v>107</v>
       </c>
-      <c r="D67" s="11">
+      <c r="D68" s="12">
         <v>105.4</v>
       </c>
-      <c r="E67" s="11">
+      <c r="E68" s="12">
         <v>105.5</v>
       </c>
-      <c r="F67" s="11">
+      <c r="F68" s="12">
         <v>102.9</v>
       </c>
-      <c r="G67" s="11">
+      <c r="G68" s="12">
         <v>105.4</v>
       </c>
-      <c r="H67" s="11">
+      <c r="H68" s="12">
         <v>112.1</v>
       </c>
-      <c r="I67" s="11">
+      <c r="I68" s="12">
         <v>105.1</v>
       </c>
-      <c r="J67" s="11">
+      <c r="J68" s="12">
         <v>108.6</v>
       </c>
-      <c r="K67" s="11">
+      <c r="K68" s="12">
         <v>108.6</v>
       </c>
-      <c r="L67" s="11">
+      <c r="L68" s="12">
         <v>125</v>
       </c>
-      <c r="M67" s="11">
+      <c r="M68" s="12">
         <v>112.6</v>
       </c>
-      <c r="N67" s="11">
+      <c r="N68" s="12">
         <v>81.8</v>
       </c>
-      <c r="O67" s="11">
+      <c r="O68" s="12">
         <v>97.4</v>
       </c>
-      <c r="P67" s="11" t="s">
-        <v>87</v>
-      </c>
-      <c r="Q67" s="11">
+      <c r="P68" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q68" s="12">
         <v>115.9</v>
       </c>
-      <c r="R67" s="11">
+      <c r="R68" s="12">
         <v>100.5</v>
       </c>
-      <c r="S67" s="11">
+      <c r="S68" s="12">
         <v>101.5</v>
       </c>
-      <c r="T67" s="11">
+      <c r="T68" s="12">
         <v>95.4</v>
       </c>
-      <c r="U67" s="11">
+      <c r="U68" s="12">
         <v>99.8</v>
       </c>
-      <c r="V67" s="11" t="s">
-        <v>87</v>
-      </c>
-      <c r="W67" s="11">
+      <c r="V68" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="W68" s="12">
         <v>106.1</v>
       </c>
-      <c r="X67" s="11">
+      <c r="X68" s="12">
         <v>93</v>
       </c>
-      <c r="Y67" s="11">
+      <c r="Y68" s="12">
         <v>133.6</v>
       </c>
-      <c r="Z67" s="11" t="s">
-        <v>87</v>
-      </c>
-      <c r="AA67" s="11" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="68" s="1" customFormat="1" ht="9.0661" customHeight="1"/>
-    <row r="69" s="1" customFormat="1" ht="122.659" customHeight="1">
-      <c r="B69" s="15" t="s">
-        <v>140</v>
-      </c>
-      <c r="C69" s="15"/>
-      <c r="D69" s="15"/>
-      <c r="E69" s="15"/>
-      <c r="F69" s="15"/>
-      <c r="G69" s="15"/>
-      <c r="H69" s="15"/>
-      <c r="I69" s="15"/>
-    </row>
+      <c r="Z68" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="AA68" s="12" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="69" s="1" customFormat="1" ht="9.0661" customHeight="1"/>
+    <row r="70" s="1" customFormat="1" ht="122.659" customHeight="1">
+      <c r="B70" s="15" t="s">
+        <v>141</v>
+      </c>
+      <c r="C70" s="15"/>
+      <c r="D70" s="15"/>
+      <c r="E70" s="15"/>
+      <c r="F70" s="15"/>
+      <c r="G70" s="15"/>
+      <c r="H70" s="15"/>
+      <c r="I70" s="15"/>
+    </row>
+    <row r="71" s="1" customFormat="1" ht="28.7982" customHeight="1"/>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="B2:I2"/>
     <mergeCell ref="B24:D24"/>
     <mergeCell ref="B4:D4"/>
     <mergeCell ref="B45:D45"/>
-    <mergeCell ref="B69:I69"/>
+    <mergeCell ref="B70:I70"/>
   </mergeCells>
   <pageSetup paperSize="121" scale="100" orientation="landscape"/>
   <headerFooter alignWithMargins="0"/>
